--- a/InputData/fuels/MPIiFI/Max Perc Inc in Fuel Imports.xlsx
+++ b/InputData/fuels/MPIiFI/Max Perc Inc in Fuel Imports.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="21328"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\deept\OneDrive\Desktop\Input Data for India 2.0\fuels\MPIiFI\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dropbox (Energy Innovation)\EI-PlcyMdl\eps-1.5.0-us-wipM\InputData\fuels\MPIiFI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E869EC3-F3C1-4E15-8C76-14C794392B21}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="41" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28185" windowHeight="12510"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -26,7 +25,13 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
+  <si>
+    <t>Source:</t>
+  </si>
+  <si>
+    <t>none needed for U.S.</t>
+  </si>
   <si>
     <t>Notes</t>
   </si>
@@ -112,74 +117,20 @@
     <t>terminal or trans-border pipeline capacity.</t>
   </si>
   <si>
+    <t>For the U.S., we do not wish to impose a cap,</t>
+  </si>
+  <si>
+    <t>so we pick an arbitrarily high percentage.</t>
+  </si>
+  <si>
     <t>Alternatively, it may reflect a legislative cap on imports.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Govt. of India has accepted a committee report to develop a roadmap </t>
-  </si>
-  <si>
-    <t xml:space="preserve">for reducing oil dependence by 10% by 2021-22 (Source 1). </t>
-  </si>
-  <si>
-    <t xml:space="preserve">However, in the past 5 years, oil import dependence has been </t>
-  </si>
-  <si>
-    <t xml:space="preserve">steadily increasing (Source 2). Further, there is no official policy </t>
-  </si>
-  <si>
-    <t>the official target and the associated roadmap.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hence, we do not impose a cap as it would be an unrealistic </t>
-  </si>
-  <si>
-    <t>high percentage.</t>
-  </si>
-  <si>
-    <t>estimate for the near- and mid-term, and pick an arbitratily</t>
-  </si>
-  <si>
-    <t>Source 1):</t>
-  </si>
-  <si>
-    <t>Import/Export of Oil</t>
-  </si>
-  <si>
-    <t>Ministry of Petroleum and Natural Gas/Press Information Bureau</t>
-  </si>
-  <si>
-    <t>https://pib.gov.in/PressReleaseIframePage.aspx?PRID=1576407</t>
-  </si>
-  <si>
-    <t>2)</t>
-  </si>
-  <si>
-    <t>Lok Sabha Unstarred Questions</t>
-  </si>
-  <si>
-    <t>Import of Oil and Gas/Unstarred Question No. 178</t>
-  </si>
-  <si>
-    <t>http://164.100.24.220/loksabhaquestions/annex/172/AU178.pdf</t>
-  </si>
-  <si>
-    <t>Ques (a), Page 1; Ans (a), Page 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">document, apart from press communication, which commits </t>
-  </si>
-  <si>
-    <t>Source 1: MoPNG/PIB</t>
-  </si>
-  <si>
-    <t>Source 2: Lok Sabha Unstarred Ques. 178</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -195,16 +146,8 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -214,12 +157,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.249977111117893"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.34998626667073579"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -233,11 +170,10 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -253,16 +189,8 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -276,99 +204,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>7887</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>19049</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>296495</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>133890</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{45ED1B56-EC6B-4BA2-85EC-1BCCB92B146C}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="5360937" y="1543049"/>
-          <a:ext cx="4555808" cy="2019841"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>238124</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>65633</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>162921</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>181343</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Picture 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{48865B98-B339-4EC9-8A8F-BDC5BE15F844}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="5343524" y="4066133"/>
-          <a:ext cx="4439647" cy="1639710"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -633,158 +468,71 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E31"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="58.28515625" customWidth="1"/>
-    <col min="4" max="4" width="3.7109375" customWidth="1"/>
-    <col min="5" max="5" width="64" customWidth="1"/>
-  </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B3" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="E3" s="10" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B4" s="9">
-        <v>2019</v>
-      </c>
-      <c r="E4" s="9">
-        <v>2019</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B5" t="s">
-        <v>38</v>
-      </c>
-      <c r="E5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B6" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="E6" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="E7" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="B3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>46</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="E31" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="B6" r:id="rId1" xr:uid="{F69D1360-ABA3-4F0A-9F18-2186723FF7F0}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId2"/>
-  <drawing r:id="rId3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="8" tint="-0.249977111117893"/>
   </sheetPr>
@@ -796,7 +544,7 @@
   <sheetData>
     <row r="1" spans="1:35" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B1" s="3">
         <v>2017</v>
@@ -903,7 +651,7 @@
     </row>
     <row r="2" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B2" s="6">
         <v>0</v>
@@ -1010,7 +758,7 @@
     </row>
     <row r="3" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B3">
         <v>999</v>
@@ -1117,7 +865,7 @@
     </row>
     <row r="4" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B4">
         <v>999</v>
@@ -1224,7 +972,7 @@
     </row>
     <row r="5" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B5">
         <v>999</v>
@@ -1331,7 +1079,7 @@
     </row>
     <row r="6" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B6" s="6">
         <v>0</v>
@@ -1438,7 +1186,7 @@
     </row>
     <row r="7" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B7" s="6">
         <v>0</v>
@@ -1545,7 +1293,7 @@
     </row>
     <row r="8" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B8" s="6">
         <v>0</v>
@@ -1652,7 +1400,7 @@
     </row>
     <row r="9" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B9">
         <v>999</v>
@@ -1759,7 +1507,7 @@
     </row>
     <row r="10" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B10">
         <v>999</v>
@@ -1866,7 +1614,7 @@
     </row>
     <row r="11" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B11">
         <v>999</v>
@@ -1973,7 +1721,7 @@
     </row>
     <row r="12" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B12">
         <v>999</v>
@@ -2080,7 +1828,7 @@
     </row>
     <row r="13" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B13">
         <v>999</v>
@@ -2187,7 +1935,7 @@
     </row>
     <row r="14" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B14">
         <v>999</v>
@@ -2294,7 +2042,7 @@
     </row>
     <row r="15" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B15" s="6">
         <v>0</v>
@@ -2401,7 +2149,7 @@
     </row>
     <row r="16" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B16" s="6">
         <v>0</v>
@@ -2508,7 +2256,7 @@
     </row>
     <row r="17" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B17">
         <v>999</v>
@@ -2615,7 +2363,7 @@
     </row>
     <row r="18" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B18">
         <v>999</v>
@@ -2722,7 +2470,7 @@
     </row>
     <row r="19" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B19">
         <v>999</v>
@@ -2829,7 +2577,7 @@
     </row>
     <row r="20" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B20">
         <v>999</v>
@@ -2936,7 +2684,7 @@
     </row>
     <row r="21" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B21">
         <v>999</v>
@@ -3043,7 +2791,7 @@
     </row>
     <row r="22" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B22">
         <v>999</v>

--- a/InputData/fuels/MPIiFI/Max Perc Inc in Fuel Imports.xlsx
+++ b/InputData/fuels/MPIiFI/Max Perc Inc in Fuel Imports.xlsx
@@ -1,41 +1,131 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27421"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dropbox (Energy Innovation)\EI-PlcyMdl\eps-1.5.0-us-wipM\InputData\fuels\MPIiFI\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://onewri-my.sharepoint.com/personal/shruti_dayal_wri_org/Documents/Desktop/Fuels updated files/"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="66" documentId="11_33D10F597B15C66183D560A425476265C6ABD3FD" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{92597CBD-054B-4703-8949-861BB93948A6}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28185" windowHeight="12510"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
     <sheet name="MPIiFI" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
-  <si>
-    <t>Source:</t>
-  </si>
-  <si>
-    <t>none needed for U.S.</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="50">
+  <si>
+    <t>MPIiFI Maximum Percentage Increase in Fuel Imports</t>
+  </si>
+  <si>
+    <t>Source 1):</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lok Sabha Secretariat </t>
+  </si>
+  <si>
+    <t>2)</t>
+  </si>
+  <si>
+    <t>Ministry of Petroleum and Natural Gas/Press Information Bureau</t>
+  </si>
+  <si>
+    <t>Review of Policy on import of crude oil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Import/Export of Natural gas </t>
+  </si>
+  <si>
+    <t>https://sansad.in/getFile/lsscommittee/Petroleum%20&amp;%20Natural%20Gas/17_Petroleum_And_Natural_Gas_23.pdf?source=loksabhadocs</t>
+  </si>
+  <si>
+    <t>https://pib.gov.in/PressReleseDetail.aspx?PRID=1881748</t>
   </si>
   <si>
     <t>Notes</t>
   </si>
   <si>
+    <t>This variable allows you to specify a cap on how much fuel imports</t>
+  </si>
+  <si>
+    <t>may increase in response to policies.</t>
+  </si>
+  <si>
+    <t>This can reflect physical constraints on imports, such as limited</t>
+  </si>
+  <si>
+    <t>terminal or trans-border pipeline capacity.</t>
+  </si>
+  <si>
+    <t>Alternatively, it may reflect a legislative cap on imports.</t>
+  </si>
+  <si>
+    <t>For the U.S., we do not wish to impose a cap,</t>
+  </si>
+  <si>
+    <t>so we pick an arbitrarily high percentage.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Govt. of India has accepted a committee report to develop a roadmap </t>
+  </si>
+  <si>
+    <t xml:space="preserve">for reducing oil dependence by 10% by 2021-22 (Source 1). </t>
+  </si>
+  <si>
+    <t xml:space="preserve">However, in the past 5 years, oil import dependence has been </t>
+  </si>
+  <si>
+    <t xml:space="preserve">steadily increasing (Source 2). Further, there is no official policy </t>
+  </si>
+  <si>
+    <t xml:space="preserve">document, apart from press communication, which commits </t>
+  </si>
+  <si>
+    <t>the official target and the associated roadmap.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Source 1) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hence, we do not impose a cap as it would be an unrealistic </t>
+  </si>
+  <si>
+    <t>estimate for the near- and mid-term, and pick an arbitratily</t>
+  </si>
+  <si>
+    <t>high percentage.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Source 2) </t>
+  </si>
+  <si>
+    <t>Max Percentage Increase (dimensionless)</t>
+  </si>
+  <si>
     <t>electricity (not used in this variable)</t>
   </si>
   <si>
@@ -97,40 +187,13 @@
   </si>
   <si>
     <t>hydrogen</t>
-  </si>
-  <si>
-    <t>Max Percentage Increase (dimensionless)</t>
-  </si>
-  <si>
-    <t>may increase in response to policies.</t>
-  </si>
-  <si>
-    <t>MPIiFI Maximum Percentage Increase in Fuel Imports</t>
-  </si>
-  <si>
-    <t>This variable allows you to specify a cap on how much fuel imports</t>
-  </si>
-  <si>
-    <t>This can reflect physical constraints on imports, such as limited</t>
-  </si>
-  <si>
-    <t>terminal or trans-border pipeline capacity.</t>
-  </si>
-  <si>
-    <t>For the U.S., we do not wish to impose a cap,</t>
-  </si>
-  <si>
-    <t>so we pick an arbitrarily high percentage.</t>
-  </si>
-  <si>
-    <t>Alternatively, it may reflect a legislative cap on imports.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -146,8 +209,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -157,6 +228,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.34998626667073579"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -170,27 +247,42 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -204,6 +296,141 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>361950</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>159461</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>482600</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>151994</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BFA764DB-8404-F309-BF73-F9150CA2DC62}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill rotWithShape="1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:srcRect t="21630" r="4110"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4629150" y="3461461"/>
+          <a:ext cx="5016500" cy="1300633"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>514350</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>6350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>377508</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>121191</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A6E668BF-E165-4593-867B-AAEEA4599A9C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4781550" y="1466850"/>
+          <a:ext cx="4759008" cy="1956341"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>241300</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>76981</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>577850</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>12409</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EA684E3A-179A-4D6E-0507-F8F3F682E6B1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill rotWithShape="1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:srcRect t="13462"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4508500" y="5080781"/>
+          <a:ext cx="5232400" cy="1040328"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -468,297 +695,411 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:O34"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
+  <cols>
+    <col min="13" max="13" width="17.7109375" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13">
       <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" ht="15.6" customHeight="1">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="11"/>
+      <c r="D3" s="11"/>
+      <c r="E3" s="11"/>
+      <c r="I3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J3" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="K3" s="8"/>
+      <c r="L3" s="8"/>
+      <c r="M3" s="8"/>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="B4" s="6">
+        <v>2023</v>
+      </c>
+      <c r="J4" s="6">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="B5" t="s">
+        <v>5</v>
+      </c>
+      <c r="J5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="B6" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="10"/>
+      <c r="D6" s="10"/>
+      <c r="E6" s="10"/>
+      <c r="J6" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="A10" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13">
+      <c r="A11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13">
+      <c r="A12" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13">
+      <c r="A13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13">
+      <c r="A14" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13">
+      <c r="A16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="30.6" customHeight="1"/>
+    <row r="19" spans="1:8">
+      <c r="A19" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
+      <c r="A20" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
+      <c r="A21" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
+      <c r="A22" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
+      <c r="A23" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
+      <c r="A24" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
+      <c r="H25" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
+      <c r="A26" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8">
+      <c r="A27" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8">
+      <c r="A28" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+    <row r="33" spans="8:15">
+      <c r="I33" s="9"/>
+      <c r="J33" s="9"/>
+      <c r="K33" s="9"/>
+      <c r="L33" s="9"/>
+      <c r="M33" s="9"/>
+      <c r="N33" s="9"/>
+      <c r="O33" s="9"/>
+    </row>
+    <row r="34" spans="8:15">
+      <c r="H34" s="1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>31</v>
-      </c>
-    </row>
   </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="J3:M3"/>
+    <mergeCell ref="I33:O33"/>
+    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="B3:E3"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <tabColor theme="8" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:AI22"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="36.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:35">
       <c r="A1" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B1" s="3">
         <v>2017</v>
       </c>
-      <c r="C1" s="4">
+      <c r="C1">
         <v>2018</v>
       </c>
       <c r="D1" s="3">
         <v>2019</v>
       </c>
-      <c r="E1" s="4">
+      <c r="E1">
         <v>2020</v>
       </c>
       <c r="F1" s="3">
         <v>2021</v>
       </c>
-      <c r="G1" s="4">
+      <c r="G1">
         <v>2022</v>
       </c>
       <c r="H1" s="3">
         <v>2023</v>
       </c>
-      <c r="I1" s="4">
+      <c r="I1">
         <v>2024</v>
       </c>
       <c r="J1" s="3">
         <v>2025</v>
       </c>
-      <c r="K1" s="4">
+      <c r="K1">
         <v>2026</v>
       </c>
       <c r="L1" s="3">
         <v>2027</v>
       </c>
-      <c r="M1" s="4">
+      <c r="M1">
         <v>2028</v>
       </c>
       <c r="N1" s="3">
         <v>2029</v>
       </c>
-      <c r="O1" s="4">
+      <c r="O1">
         <v>2030</v>
       </c>
       <c r="P1" s="3">
         <v>2031</v>
       </c>
-      <c r="Q1" s="4">
+      <c r="Q1">
         <v>2032</v>
       </c>
       <c r="R1" s="3">
         <v>2033</v>
       </c>
-      <c r="S1" s="4">
+      <c r="S1">
         <v>2034</v>
       </c>
       <c r="T1" s="3">
         <v>2035</v>
       </c>
-      <c r="U1" s="4">
+      <c r="U1">
         <v>2036</v>
       </c>
       <c r="V1" s="3">
         <v>2037</v>
       </c>
-      <c r="W1" s="4">
+      <c r="W1">
         <v>2038</v>
       </c>
       <c r="X1" s="3">
         <v>2039</v>
       </c>
-      <c r="Y1" s="4">
+      <c r="Y1">
         <v>2040</v>
       </c>
       <c r="Z1" s="3">
         <v>2041</v>
       </c>
-      <c r="AA1" s="4">
+      <c r="AA1">
         <v>2042</v>
       </c>
       <c r="AB1" s="3">
         <v>2043</v>
       </c>
-      <c r="AC1" s="4">
+      <c r="AC1">
         <v>2044</v>
       </c>
       <c r="AD1" s="3">
         <v>2045</v>
       </c>
-      <c r="AE1" s="4">
+      <c r="AE1">
         <v>2046</v>
       </c>
       <c r="AF1" s="3">
         <v>2047</v>
       </c>
-      <c r="AG1" s="4">
+      <c r="AG1">
         <v>2048</v>
       </c>
       <c r="AH1" s="3">
         <v>2049</v>
       </c>
-      <c r="AI1" s="4">
+      <c r="AI1">
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A2" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="6">
-        <v>0</v>
-      </c>
-      <c r="C2" s="6">
-        <v>0</v>
-      </c>
-      <c r="D2" s="6">
-        <v>0</v>
-      </c>
-      <c r="E2" s="6">
-        <v>0</v>
-      </c>
-      <c r="F2" s="6">
-        <v>0</v>
-      </c>
-      <c r="G2" s="6">
-        <v>0</v>
-      </c>
-      <c r="H2" s="6">
-        <v>0</v>
-      </c>
-      <c r="I2" s="6">
-        <v>0</v>
-      </c>
-      <c r="J2" s="6">
-        <v>0</v>
-      </c>
-      <c r="K2" s="6">
-        <v>0</v>
-      </c>
-      <c r="L2" s="6">
-        <v>0</v>
-      </c>
-      <c r="M2" s="6">
-        <v>0</v>
-      </c>
-      <c r="N2" s="6">
-        <v>0</v>
-      </c>
-      <c r="O2" s="6">
-        <v>0</v>
-      </c>
-      <c r="P2" s="6">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="6">
-        <v>0</v>
-      </c>
-      <c r="R2" s="6">
-        <v>0</v>
-      </c>
-      <c r="S2" s="6">
-        <v>0</v>
-      </c>
-      <c r="T2" s="6">
-        <v>0</v>
-      </c>
-      <c r="U2" s="6">
-        <v>0</v>
-      </c>
-      <c r="V2" s="6">
-        <v>0</v>
-      </c>
-      <c r="W2" s="6">
-        <v>0</v>
-      </c>
-      <c r="X2" s="6">
-        <v>0</v>
-      </c>
-      <c r="Y2" s="6">
-        <v>0</v>
-      </c>
-      <c r="Z2" s="6">
-        <v>0</v>
-      </c>
-      <c r="AA2" s="6">
-        <v>0</v>
-      </c>
-      <c r="AB2" s="6">
-        <v>0</v>
-      </c>
-      <c r="AC2" s="6">
-        <v>0</v>
-      </c>
-      <c r="AD2" s="6">
-        <v>0</v>
-      </c>
-      <c r="AE2" s="6">
-        <v>0</v>
-      </c>
-      <c r="AF2" s="6">
-        <v>0</v>
-      </c>
-      <c r="AG2" s="6">
-        <v>0</v>
-      </c>
-      <c r="AH2" s="6">
-        <v>0</v>
-      </c>
-      <c r="AI2" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
-        <v>4</v>
+    <row r="2" spans="1:35">
+      <c r="A2" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B2" s="4">
+        <v>0</v>
+      </c>
+      <c r="C2" s="4">
+        <v>0</v>
+      </c>
+      <c r="D2" s="4">
+        <v>0</v>
+      </c>
+      <c r="E2" s="4">
+        <v>0</v>
+      </c>
+      <c r="F2" s="4">
+        <v>0</v>
+      </c>
+      <c r="G2" s="4">
+        <v>0</v>
+      </c>
+      <c r="H2" s="4">
+        <v>0</v>
+      </c>
+      <c r="I2" s="4">
+        <v>0</v>
+      </c>
+      <c r="J2" s="4">
+        <v>0</v>
+      </c>
+      <c r="K2" s="4">
+        <v>0</v>
+      </c>
+      <c r="L2" s="4">
+        <v>0</v>
+      </c>
+      <c r="M2" s="4">
+        <v>0</v>
+      </c>
+      <c r="N2" s="4">
+        <v>0</v>
+      </c>
+      <c r="O2" s="4">
+        <v>0</v>
+      </c>
+      <c r="P2" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="4">
+        <v>0</v>
+      </c>
+      <c r="R2" s="4">
+        <v>0</v>
+      </c>
+      <c r="S2" s="4">
+        <v>0</v>
+      </c>
+      <c r="T2" s="4">
+        <v>0</v>
+      </c>
+      <c r="U2" s="4">
+        <v>0</v>
+      </c>
+      <c r="V2" s="4">
+        <v>0</v>
+      </c>
+      <c r="W2" s="4">
+        <v>0</v>
+      </c>
+      <c r="X2" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y2" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z2" s="4">
+        <v>0</v>
+      </c>
+      <c r="AA2" s="4">
+        <v>0</v>
+      </c>
+      <c r="AB2" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC2" s="4">
+        <v>0</v>
+      </c>
+      <c r="AD2" s="4">
+        <v>0</v>
+      </c>
+      <c r="AE2" s="4">
+        <v>0</v>
+      </c>
+      <c r="AF2" s="4">
+        <v>0</v>
+      </c>
+      <c r="AG2" s="4">
+        <v>0</v>
+      </c>
+      <c r="AH2" s="4">
+        <v>0</v>
+      </c>
+      <c r="AI2" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:35">
+      <c r="A3" t="s">
+        <v>30</v>
       </c>
       <c r="B3">
         <v>999</v>
@@ -863,9 +1204,9 @@
         <v>999</v>
       </c>
     </row>
-    <row r="4" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
-        <v>5</v>
+    <row r="4" spans="1:35">
+      <c r="A4" t="s">
+        <v>31</v>
       </c>
       <c r="B4">
         <v>999</v>
@@ -970,9 +1311,9 @@
         <v>999</v>
       </c>
     </row>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
-        <v>6</v>
+    <row r="5" spans="1:35">
+      <c r="A5" t="s">
+        <v>32</v>
       </c>
       <c r="B5">
         <v>999</v>
@@ -1077,330 +1418,330 @@
         <v>999</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A6" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" s="6">
-        <v>0</v>
-      </c>
-      <c r="C6" s="6">
-        <v>0</v>
-      </c>
-      <c r="D6" s="6">
-        <v>0</v>
-      </c>
-      <c r="E6" s="6">
-        <v>0</v>
-      </c>
-      <c r="F6" s="6">
-        <v>0</v>
-      </c>
-      <c r="G6" s="6">
-        <v>0</v>
-      </c>
-      <c r="H6" s="6">
-        <v>0</v>
-      </c>
-      <c r="I6" s="6">
-        <v>0</v>
-      </c>
-      <c r="J6" s="6">
-        <v>0</v>
-      </c>
-      <c r="K6" s="6">
-        <v>0</v>
-      </c>
-      <c r="L6" s="6">
-        <v>0</v>
-      </c>
-      <c r="M6" s="6">
-        <v>0</v>
-      </c>
-      <c r="N6" s="6">
-        <v>0</v>
-      </c>
-      <c r="O6" s="6">
-        <v>0</v>
-      </c>
-      <c r="P6" s="6">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="6">
-        <v>0</v>
-      </c>
-      <c r="R6" s="6">
-        <v>0</v>
-      </c>
-      <c r="S6" s="6">
-        <v>0</v>
-      </c>
-      <c r="T6" s="6">
-        <v>0</v>
-      </c>
-      <c r="U6" s="6">
-        <v>0</v>
-      </c>
-      <c r="V6" s="6">
-        <v>0</v>
-      </c>
-      <c r="W6" s="6">
-        <v>0</v>
-      </c>
-      <c r="X6" s="6">
-        <v>0</v>
-      </c>
-      <c r="Y6" s="6">
-        <v>0</v>
-      </c>
-      <c r="Z6" s="6">
-        <v>0</v>
-      </c>
-      <c r="AA6" s="6">
-        <v>0</v>
-      </c>
-      <c r="AB6" s="6">
-        <v>0</v>
-      </c>
-      <c r="AC6" s="6">
-        <v>0</v>
-      </c>
-      <c r="AD6" s="6">
-        <v>0</v>
-      </c>
-      <c r="AE6" s="6">
-        <v>0</v>
-      </c>
-      <c r="AF6" s="6">
-        <v>0</v>
-      </c>
-      <c r="AG6" s="6">
-        <v>0</v>
-      </c>
-      <c r="AH6" s="6">
-        <v>0</v>
-      </c>
-      <c r="AI6" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A7" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" s="6">
-        <v>0</v>
-      </c>
-      <c r="C7" s="6">
-        <v>0</v>
-      </c>
-      <c r="D7" s="6">
-        <v>0</v>
-      </c>
-      <c r="E7" s="6">
-        <v>0</v>
-      </c>
-      <c r="F7" s="6">
-        <v>0</v>
-      </c>
-      <c r="G7" s="6">
-        <v>0</v>
-      </c>
-      <c r="H7" s="6">
-        <v>0</v>
-      </c>
-      <c r="I7" s="6">
-        <v>0</v>
-      </c>
-      <c r="J7" s="6">
-        <v>0</v>
-      </c>
-      <c r="K7" s="6">
-        <v>0</v>
-      </c>
-      <c r="L7" s="6">
-        <v>0</v>
-      </c>
-      <c r="M7" s="6">
-        <v>0</v>
-      </c>
-      <c r="N7" s="6">
-        <v>0</v>
-      </c>
-      <c r="O7" s="6">
-        <v>0</v>
-      </c>
-      <c r="P7" s="6">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="6">
-        <v>0</v>
-      </c>
-      <c r="R7" s="6">
-        <v>0</v>
-      </c>
-      <c r="S7" s="6">
-        <v>0</v>
-      </c>
-      <c r="T7" s="6">
-        <v>0</v>
-      </c>
-      <c r="U7" s="6">
-        <v>0</v>
-      </c>
-      <c r="V7" s="6">
-        <v>0</v>
-      </c>
-      <c r="W7" s="6">
-        <v>0</v>
-      </c>
-      <c r="X7" s="6">
-        <v>0</v>
-      </c>
-      <c r="Y7" s="6">
-        <v>0</v>
-      </c>
-      <c r="Z7" s="6">
-        <v>0</v>
-      </c>
-      <c r="AA7" s="6">
-        <v>0</v>
-      </c>
-      <c r="AB7" s="6">
-        <v>0</v>
-      </c>
-      <c r="AC7" s="6">
-        <v>0</v>
-      </c>
-      <c r="AD7" s="6">
-        <v>0</v>
-      </c>
-      <c r="AE7" s="6">
-        <v>0</v>
-      </c>
-      <c r="AF7" s="6">
-        <v>0</v>
-      </c>
-      <c r="AG7" s="6">
-        <v>0</v>
-      </c>
-      <c r="AH7" s="6">
-        <v>0</v>
-      </c>
-      <c r="AI7" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A8" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" s="6">
-        <v>0</v>
-      </c>
-      <c r="C8" s="6">
-        <v>0</v>
-      </c>
-      <c r="D8" s="6">
-        <v>0</v>
-      </c>
-      <c r="E8" s="6">
-        <v>0</v>
-      </c>
-      <c r="F8" s="6">
-        <v>0</v>
-      </c>
-      <c r="G8" s="6">
-        <v>0</v>
-      </c>
-      <c r="H8" s="6">
-        <v>0</v>
-      </c>
-      <c r="I8" s="6">
-        <v>0</v>
-      </c>
-      <c r="J8" s="6">
-        <v>0</v>
-      </c>
-      <c r="K8" s="6">
-        <v>0</v>
-      </c>
-      <c r="L8" s="6">
-        <v>0</v>
-      </c>
-      <c r="M8" s="6">
-        <v>0</v>
-      </c>
-      <c r="N8" s="6">
-        <v>0</v>
-      </c>
-      <c r="O8" s="6">
-        <v>0</v>
-      </c>
-      <c r="P8" s="6">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="6">
-        <v>0</v>
-      </c>
-      <c r="R8" s="6">
-        <v>0</v>
-      </c>
-      <c r="S8" s="6">
-        <v>0</v>
-      </c>
-      <c r="T8" s="6">
-        <v>0</v>
-      </c>
-      <c r="U8" s="6">
-        <v>0</v>
-      </c>
-      <c r="V8" s="6">
-        <v>0</v>
-      </c>
-      <c r="W8" s="6">
-        <v>0</v>
-      </c>
-      <c r="X8" s="6">
-        <v>0</v>
-      </c>
-      <c r="Y8" s="6">
-        <v>0</v>
-      </c>
-      <c r="Z8" s="6">
-        <v>0</v>
-      </c>
-      <c r="AA8" s="6">
-        <v>0</v>
-      </c>
-      <c r="AB8" s="6">
-        <v>0</v>
-      </c>
-      <c r="AC8" s="6">
-        <v>0</v>
-      </c>
-      <c r="AD8" s="6">
-        <v>0</v>
-      </c>
-      <c r="AE8" s="6">
-        <v>0</v>
-      </c>
-      <c r="AF8" s="6">
-        <v>0</v>
-      </c>
-      <c r="AG8" s="6">
-        <v>0</v>
-      </c>
-      <c r="AH8" s="6">
-        <v>0</v>
-      </c>
-      <c r="AI8" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A9" s="5" t="s">
-        <v>10</v>
+    <row r="6" spans="1:35">
+      <c r="A6" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6" s="4">
+        <v>0</v>
+      </c>
+      <c r="C6" s="4">
+        <v>0</v>
+      </c>
+      <c r="D6" s="4">
+        <v>0</v>
+      </c>
+      <c r="E6" s="4">
+        <v>0</v>
+      </c>
+      <c r="F6" s="4">
+        <v>0</v>
+      </c>
+      <c r="G6" s="4">
+        <v>0</v>
+      </c>
+      <c r="H6" s="4">
+        <v>0</v>
+      </c>
+      <c r="I6" s="4">
+        <v>0</v>
+      </c>
+      <c r="J6" s="4">
+        <v>0</v>
+      </c>
+      <c r="K6" s="4">
+        <v>0</v>
+      </c>
+      <c r="L6" s="4">
+        <v>0</v>
+      </c>
+      <c r="M6" s="4">
+        <v>0</v>
+      </c>
+      <c r="N6" s="4">
+        <v>0</v>
+      </c>
+      <c r="O6" s="4">
+        <v>0</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0</v>
+      </c>
+      <c r="R6" s="4">
+        <v>0</v>
+      </c>
+      <c r="S6" s="4">
+        <v>0</v>
+      </c>
+      <c r="T6" s="4">
+        <v>0</v>
+      </c>
+      <c r="U6" s="4">
+        <v>0</v>
+      </c>
+      <c r="V6" s="4">
+        <v>0</v>
+      </c>
+      <c r="W6" s="4">
+        <v>0</v>
+      </c>
+      <c r="X6" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z6" s="4">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="4">
+        <v>0</v>
+      </c>
+      <c r="AB6" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC6" s="4">
+        <v>0</v>
+      </c>
+      <c r="AD6" s="4">
+        <v>0</v>
+      </c>
+      <c r="AE6" s="4">
+        <v>0</v>
+      </c>
+      <c r="AF6" s="4">
+        <v>0</v>
+      </c>
+      <c r="AG6" s="4">
+        <v>0</v>
+      </c>
+      <c r="AH6" s="4">
+        <v>0</v>
+      </c>
+      <c r="AI6" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:35">
+      <c r="A7" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B7" s="4">
+        <v>0</v>
+      </c>
+      <c r="C7" s="4">
+        <v>0</v>
+      </c>
+      <c r="D7" s="4">
+        <v>0</v>
+      </c>
+      <c r="E7" s="4">
+        <v>0</v>
+      </c>
+      <c r="F7" s="4">
+        <v>0</v>
+      </c>
+      <c r="G7" s="4">
+        <v>0</v>
+      </c>
+      <c r="H7" s="4">
+        <v>0</v>
+      </c>
+      <c r="I7" s="4">
+        <v>0</v>
+      </c>
+      <c r="J7" s="4">
+        <v>0</v>
+      </c>
+      <c r="K7" s="4">
+        <v>0</v>
+      </c>
+      <c r="L7" s="4">
+        <v>0</v>
+      </c>
+      <c r="M7" s="4">
+        <v>0</v>
+      </c>
+      <c r="N7" s="4">
+        <v>0</v>
+      </c>
+      <c r="O7" s="4">
+        <v>0</v>
+      </c>
+      <c r="P7" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>0</v>
+      </c>
+      <c r="R7" s="4">
+        <v>0</v>
+      </c>
+      <c r="S7" s="4">
+        <v>0</v>
+      </c>
+      <c r="T7" s="4">
+        <v>0</v>
+      </c>
+      <c r="U7" s="4">
+        <v>0</v>
+      </c>
+      <c r="V7" s="4">
+        <v>0</v>
+      </c>
+      <c r="W7" s="4">
+        <v>0</v>
+      </c>
+      <c r="X7" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z7" s="4">
+        <v>0</v>
+      </c>
+      <c r="AA7" s="4">
+        <v>0</v>
+      </c>
+      <c r="AB7" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC7" s="4">
+        <v>0</v>
+      </c>
+      <c r="AD7" s="4">
+        <v>0</v>
+      </c>
+      <c r="AE7" s="4">
+        <v>0</v>
+      </c>
+      <c r="AF7" s="4">
+        <v>0</v>
+      </c>
+      <c r="AG7" s="4">
+        <v>0</v>
+      </c>
+      <c r="AH7" s="4">
+        <v>0</v>
+      </c>
+      <c r="AI7" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:35">
+      <c r="A8" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B8" s="4">
+        <v>0</v>
+      </c>
+      <c r="C8" s="4">
+        <v>0</v>
+      </c>
+      <c r="D8" s="4">
+        <v>0</v>
+      </c>
+      <c r="E8" s="4">
+        <v>0</v>
+      </c>
+      <c r="F8" s="4">
+        <v>0</v>
+      </c>
+      <c r="G8" s="4">
+        <v>0</v>
+      </c>
+      <c r="H8" s="4">
+        <v>0</v>
+      </c>
+      <c r="I8" s="4">
+        <v>0</v>
+      </c>
+      <c r="J8" s="4">
+        <v>0</v>
+      </c>
+      <c r="K8" s="4">
+        <v>0</v>
+      </c>
+      <c r="L8" s="4">
+        <v>0</v>
+      </c>
+      <c r="M8" s="4">
+        <v>0</v>
+      </c>
+      <c r="N8" s="4">
+        <v>0</v>
+      </c>
+      <c r="O8" s="4">
+        <v>0</v>
+      </c>
+      <c r="P8" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="4">
+        <v>0</v>
+      </c>
+      <c r="R8" s="4">
+        <v>0</v>
+      </c>
+      <c r="S8" s="4">
+        <v>0</v>
+      </c>
+      <c r="T8" s="4">
+        <v>0</v>
+      </c>
+      <c r="U8" s="4">
+        <v>0</v>
+      </c>
+      <c r="V8" s="4">
+        <v>0</v>
+      </c>
+      <c r="W8" s="4">
+        <v>0</v>
+      </c>
+      <c r="X8" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z8" s="4">
+        <v>0</v>
+      </c>
+      <c r="AA8" s="4">
+        <v>0</v>
+      </c>
+      <c r="AB8" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC8" s="4">
+        <v>0</v>
+      </c>
+      <c r="AD8" s="4">
+        <v>0</v>
+      </c>
+      <c r="AE8" s="4">
+        <v>0</v>
+      </c>
+      <c r="AF8" s="4">
+        <v>0</v>
+      </c>
+      <c r="AG8" s="4">
+        <v>0</v>
+      </c>
+      <c r="AH8" s="4">
+        <v>0</v>
+      </c>
+      <c r="AI8" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:35">
+      <c r="A9" t="s">
+        <v>36</v>
       </c>
       <c r="B9">
         <v>999</v>
@@ -1505,9 +1846,9 @@
         <v>999</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A10" s="5" t="s">
-        <v>11</v>
+    <row r="10" spans="1:35">
+      <c r="A10" t="s">
+        <v>37</v>
       </c>
       <c r="B10">
         <v>999</v>
@@ -1612,9 +1953,9 @@
         <v>999</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="s">
-        <v>12</v>
+    <row r="11" spans="1:35">
+      <c r="A11" t="s">
+        <v>38</v>
       </c>
       <c r="B11">
         <v>999</v>
@@ -1719,9 +2060,9 @@
         <v>999</v>
       </c>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="s">
-        <v>13</v>
+    <row r="12" spans="1:35">
+      <c r="A12" t="s">
+        <v>39</v>
       </c>
       <c r="B12">
         <v>999</v>
@@ -1826,9 +2167,9 @@
         <v>999</v>
       </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A13" s="5" t="s">
-        <v>14</v>
+    <row r="13" spans="1:35">
+      <c r="A13" t="s">
+        <v>40</v>
       </c>
       <c r="B13">
         <v>999</v>
@@ -1933,9 +2274,9 @@
         <v>999</v>
       </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A14" s="5" t="s">
-        <v>15</v>
+    <row r="14" spans="1:35">
+      <c r="A14" t="s">
+        <v>41</v>
       </c>
       <c r="B14">
         <v>999</v>
@@ -2040,223 +2381,223 @@
         <v>999</v>
       </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A15" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="B15" s="6">
-        <v>0</v>
-      </c>
-      <c r="C15" s="6">
-        <v>0</v>
-      </c>
-      <c r="D15" s="6">
-        <v>0</v>
-      </c>
-      <c r="E15" s="6">
-        <v>0</v>
-      </c>
-      <c r="F15" s="6">
-        <v>0</v>
-      </c>
-      <c r="G15" s="6">
-        <v>0</v>
-      </c>
-      <c r="H15" s="6">
-        <v>0</v>
-      </c>
-      <c r="I15" s="6">
-        <v>0</v>
-      </c>
-      <c r="J15" s="6">
-        <v>0</v>
-      </c>
-      <c r="K15" s="6">
-        <v>0</v>
-      </c>
-      <c r="L15" s="6">
-        <v>0</v>
-      </c>
-      <c r="M15" s="6">
-        <v>0</v>
-      </c>
-      <c r="N15" s="6">
-        <v>0</v>
-      </c>
-      <c r="O15" s="6">
-        <v>0</v>
-      </c>
-      <c r="P15" s="6">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="6">
-        <v>0</v>
-      </c>
-      <c r="R15" s="6">
-        <v>0</v>
-      </c>
-      <c r="S15" s="6">
-        <v>0</v>
-      </c>
-      <c r="T15" s="6">
-        <v>0</v>
-      </c>
-      <c r="U15" s="6">
-        <v>0</v>
-      </c>
-      <c r="V15" s="6">
-        <v>0</v>
-      </c>
-      <c r="W15" s="6">
-        <v>0</v>
-      </c>
-      <c r="X15" s="6">
-        <v>0</v>
-      </c>
-      <c r="Y15" s="6">
-        <v>0</v>
-      </c>
-      <c r="Z15" s="6">
-        <v>0</v>
-      </c>
-      <c r="AA15" s="6">
-        <v>0</v>
-      </c>
-      <c r="AB15" s="6">
-        <v>0</v>
-      </c>
-      <c r="AC15" s="6">
-        <v>0</v>
-      </c>
-      <c r="AD15" s="6">
-        <v>0</v>
-      </c>
-      <c r="AE15" s="6">
-        <v>0</v>
-      </c>
-      <c r="AF15" s="6">
-        <v>0</v>
-      </c>
-      <c r="AG15" s="6">
-        <v>0</v>
-      </c>
-      <c r="AH15" s="6">
-        <v>0</v>
-      </c>
-      <c r="AI15" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A16" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="B16" s="6">
-        <v>0</v>
-      </c>
-      <c r="C16" s="6">
-        <v>0</v>
-      </c>
-      <c r="D16" s="6">
-        <v>0</v>
-      </c>
-      <c r="E16" s="6">
-        <v>0</v>
-      </c>
-      <c r="F16" s="6">
-        <v>0</v>
-      </c>
-      <c r="G16" s="6">
-        <v>0</v>
-      </c>
-      <c r="H16" s="6">
-        <v>0</v>
-      </c>
-      <c r="I16" s="6">
-        <v>0</v>
-      </c>
-      <c r="J16" s="6">
-        <v>0</v>
-      </c>
-      <c r="K16" s="6">
-        <v>0</v>
-      </c>
-      <c r="L16" s="6">
-        <v>0</v>
-      </c>
-      <c r="M16" s="6">
-        <v>0</v>
-      </c>
-      <c r="N16" s="6">
-        <v>0</v>
-      </c>
-      <c r="O16" s="6">
-        <v>0</v>
-      </c>
-      <c r="P16" s="6">
-        <v>0</v>
-      </c>
-      <c r="Q16" s="6">
-        <v>0</v>
-      </c>
-      <c r="R16" s="6">
-        <v>0</v>
-      </c>
-      <c r="S16" s="6">
-        <v>0</v>
-      </c>
-      <c r="T16" s="6">
-        <v>0</v>
-      </c>
-      <c r="U16" s="6">
-        <v>0</v>
-      </c>
-      <c r="V16" s="6">
-        <v>0</v>
-      </c>
-      <c r="W16" s="6">
-        <v>0</v>
-      </c>
-      <c r="X16" s="6">
-        <v>0</v>
-      </c>
-      <c r="Y16" s="6">
-        <v>0</v>
-      </c>
-      <c r="Z16" s="6">
-        <v>0</v>
-      </c>
-      <c r="AA16" s="6">
-        <v>0</v>
-      </c>
-      <c r="AB16" s="6">
-        <v>0</v>
-      </c>
-      <c r="AC16" s="6">
-        <v>0</v>
-      </c>
-      <c r="AD16" s="6">
-        <v>0</v>
-      </c>
-      <c r="AE16" s="6">
-        <v>0</v>
-      </c>
-      <c r="AF16" s="6">
-        <v>0</v>
-      </c>
-      <c r="AG16" s="6">
-        <v>0</v>
-      </c>
-      <c r="AH16" s="6">
-        <v>0</v>
-      </c>
-      <c r="AI16" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A17" s="5" t="s">
-        <v>18</v>
+    <row r="15" spans="1:35">
+      <c r="A15" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B15" s="4">
+        <v>0</v>
+      </c>
+      <c r="C15" s="4">
+        <v>0</v>
+      </c>
+      <c r="D15" s="4">
+        <v>0</v>
+      </c>
+      <c r="E15" s="4">
+        <v>0</v>
+      </c>
+      <c r="F15" s="4">
+        <v>0</v>
+      </c>
+      <c r="G15" s="4">
+        <v>0</v>
+      </c>
+      <c r="H15" s="4">
+        <v>0</v>
+      </c>
+      <c r="I15" s="4">
+        <v>0</v>
+      </c>
+      <c r="J15" s="4">
+        <v>0</v>
+      </c>
+      <c r="K15" s="4">
+        <v>0</v>
+      </c>
+      <c r="L15" s="4">
+        <v>0</v>
+      </c>
+      <c r="M15" s="4">
+        <v>0</v>
+      </c>
+      <c r="N15" s="4">
+        <v>0</v>
+      </c>
+      <c r="O15" s="4">
+        <v>0</v>
+      </c>
+      <c r="P15" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="4">
+        <v>0</v>
+      </c>
+      <c r="R15" s="4">
+        <v>0</v>
+      </c>
+      <c r="S15" s="4">
+        <v>0</v>
+      </c>
+      <c r="T15" s="4">
+        <v>0</v>
+      </c>
+      <c r="U15" s="4">
+        <v>0</v>
+      </c>
+      <c r="V15" s="4">
+        <v>0</v>
+      </c>
+      <c r="W15" s="4">
+        <v>0</v>
+      </c>
+      <c r="X15" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y15" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z15" s="4">
+        <v>0</v>
+      </c>
+      <c r="AA15" s="4">
+        <v>0</v>
+      </c>
+      <c r="AB15" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC15" s="4">
+        <v>0</v>
+      </c>
+      <c r="AD15" s="4">
+        <v>0</v>
+      </c>
+      <c r="AE15" s="4">
+        <v>0</v>
+      </c>
+      <c r="AF15" s="4">
+        <v>0</v>
+      </c>
+      <c r="AG15" s="4">
+        <v>0</v>
+      </c>
+      <c r="AH15" s="4">
+        <v>0</v>
+      </c>
+      <c r="AI15" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35">
+      <c r="A16" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B16" s="4">
+        <v>0</v>
+      </c>
+      <c r="C16" s="4">
+        <v>0</v>
+      </c>
+      <c r="D16" s="4">
+        <v>0</v>
+      </c>
+      <c r="E16" s="4">
+        <v>0</v>
+      </c>
+      <c r="F16" s="4">
+        <v>0</v>
+      </c>
+      <c r="G16" s="4">
+        <v>0</v>
+      </c>
+      <c r="H16" s="4">
+        <v>0</v>
+      </c>
+      <c r="I16" s="4">
+        <v>0</v>
+      </c>
+      <c r="J16" s="4">
+        <v>0</v>
+      </c>
+      <c r="K16" s="4">
+        <v>0</v>
+      </c>
+      <c r="L16" s="4">
+        <v>0</v>
+      </c>
+      <c r="M16" s="4">
+        <v>0</v>
+      </c>
+      <c r="N16" s="4">
+        <v>0</v>
+      </c>
+      <c r="O16" s="4">
+        <v>0</v>
+      </c>
+      <c r="P16" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="4">
+        <v>0</v>
+      </c>
+      <c r="R16" s="4">
+        <v>0</v>
+      </c>
+      <c r="S16" s="4">
+        <v>0</v>
+      </c>
+      <c r="T16" s="4">
+        <v>0</v>
+      </c>
+      <c r="U16" s="4">
+        <v>0</v>
+      </c>
+      <c r="V16" s="4">
+        <v>0</v>
+      </c>
+      <c r="W16" s="4">
+        <v>0</v>
+      </c>
+      <c r="X16" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y16" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z16" s="4">
+        <v>0</v>
+      </c>
+      <c r="AA16" s="4">
+        <v>0</v>
+      </c>
+      <c r="AB16" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC16" s="4">
+        <v>0</v>
+      </c>
+      <c r="AD16" s="4">
+        <v>0</v>
+      </c>
+      <c r="AE16" s="4">
+        <v>0</v>
+      </c>
+      <c r="AF16" s="4">
+        <v>0</v>
+      </c>
+      <c r="AG16" s="4">
+        <v>0</v>
+      </c>
+      <c r="AH16" s="4">
+        <v>0</v>
+      </c>
+      <c r="AI16" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:35">
+      <c r="A17" t="s">
+        <v>44</v>
       </c>
       <c r="B17">
         <v>999</v>
@@ -2361,9 +2702,9 @@
         <v>999</v>
       </c>
     </row>
-    <row r="18" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A18" s="5" t="s">
-        <v>19</v>
+    <row r="18" spans="1:35">
+      <c r="A18" t="s">
+        <v>45</v>
       </c>
       <c r="B18">
         <v>999</v>
@@ -2468,9 +2809,9 @@
         <v>999</v>
       </c>
     </row>
-    <row r="19" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A19" s="5" t="s">
-        <v>20</v>
+    <row r="19" spans="1:35">
+      <c r="A19" t="s">
+        <v>46</v>
       </c>
       <c r="B19">
         <v>999</v>
@@ -2575,9 +2916,9 @@
         <v>999</v>
       </c>
     </row>
-    <row r="20" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A20" s="5" t="s">
-        <v>21</v>
+    <row r="20" spans="1:35">
+      <c r="A20" t="s">
+        <v>47</v>
       </c>
       <c r="B20">
         <v>999</v>
@@ -2682,9 +3023,9 @@
         <v>999</v>
       </c>
     </row>
-    <row r="21" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A21" s="5" t="s">
-        <v>22</v>
+    <row r="21" spans="1:35">
+      <c r="A21" t="s">
+        <v>48</v>
       </c>
       <c r="B21">
         <v>999</v>
@@ -2789,9 +3130,9 @@
         <v>999</v>
       </c>
     </row>
-    <row r="22" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A22" s="5" t="s">
-        <v>23</v>
+    <row r="22" spans="1:35">
+      <c r="A22" t="s">
+        <v>49</v>
       </c>
       <c r="B22">
         <v>999</v>
@@ -2899,4 +3240,175 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A251C7805F896F47A4F48569C73A0799" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="77cd1fc208aa16a525090c2a27f33c66">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f3083de3-5d4e-49f2-a3cd-0aeb079e6739" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d77402130d0e9b5bbfbb66ed18db98d9" ns2:_="">
+    <xsd:import namespace="f3083de3-5d4e-49f2-a3cd-0aeb079e6739"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="f3083de3-5d4e-49f2-a3cd-0aeb079e6739" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="10" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="11" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E6E21EF9-3597-4776-94A2-FCE75ED38552}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{26A12603-A1C6-4C16-B39B-2FBB0D21E2F7}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{817666BC-9565-4828-BBFE-F5632693316E}"/>
 </file>